--- a/language/da-dialekter_DA.xlsx
+++ b/language/da-dialekter_DA.xlsx
@@ -172,7 +172,7 @@
     <t>Gøtudanskt (særlig skandinavisk udtaleform på Færøerne)</t>
   </si>
   <si>
-    <t>Gøtudanskt</t>
+    <t>Andet</t>
   </si>
   <si>
     <t>Rigsdansk</t>
